--- a/dataset_t6_grouped/results2/G1/G1_T0374_W0017F0001T0006Z000C1N30_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G1/G1_T0374_W0017F0001T0006Z000C1N30_analysis.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H13"/>
+  <dimension ref="A1:H14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -486,10 +486,10 @@
         <v>105.3942007704006</v>
       </c>
       <c r="E2" t="n">
-        <v>26.45229551864099</v>
+        <v>25.43425113145828</v>
       </c>
       <c r="F2" t="n">
-        <v>26.6957650274269</v>
+        <v>25.67704896844508</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -518,10 +518,10 @@
         <v>35.15542394787635</v>
       </c>
       <c r="E3" t="n">
-        <v>26.45229551864099</v>
+        <v>25.43425113145828</v>
       </c>
       <c r="F3" t="n">
-        <v>26.6957650274269</v>
+        <v>25.67704896844508</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -550,10 +550,10 @@
         <v>29.56470169759898</v>
       </c>
       <c r="E4" t="n">
-        <v>26.45229551864099</v>
+        <v>25.43425113145828</v>
       </c>
       <c r="F4" t="n">
-        <v>26.6957650274269</v>
+        <v>25.67704896844508</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -582,10 +582,10 @@
         <v>20.84778765253281</v>
       </c>
       <c r="E5" t="n">
-        <v>26.45229551864099</v>
+        <v>25.43425113145828</v>
       </c>
       <c r="F5" t="n">
-        <v>26.6957650274269</v>
+        <v>25.67704896844508</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -614,10 +614,10 @@
         <v>28.30451177599641</v>
       </c>
       <c r="E6" t="n">
-        <v>26.45229551864099</v>
+        <v>25.43425113145828</v>
       </c>
       <c r="F6" t="n">
-        <v>26.6957650274269</v>
+        <v>25.67704896844508</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>10.72170223799552</v>
+        <v>35.52178965868286</v>
       </c>
       <c r="D7" t="n">
-        <v>12.14657995092263</v>
+        <v>35.96971709957152</v>
       </c>
       <c r="E7" t="n">
-        <v>26.45229551864099</v>
+        <v>25.43425113145828</v>
       </c>
       <c r="F7" t="n">
-        <v>26.6957650274269</v>
+        <v>25.67704896844508</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>5.787569291502646</v>
+        <v>10.72170223799552</v>
       </c>
       <c r="D8" t="n">
-        <v>4.657974012814054</v>
+        <v>12.14657995092263</v>
       </c>
       <c r="E8" t="n">
-        <v>26.45229551864099</v>
+        <v>25.43425113145828</v>
       </c>
       <c r="F8" t="n">
-        <v>26.6957650274269</v>
+        <v>25.67704896844508</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>6.039610913446428</v>
+        <v>5.787569291502646</v>
       </c>
       <c r="D9" t="n">
-        <v>7.674684372183226</v>
+        <v>4.657974012814054</v>
       </c>
       <c r="E9" t="n">
-        <v>26.45229551864099</v>
+        <v>25.43425113145828</v>
       </c>
       <c r="F9" t="n">
-        <v>26.6957650274269</v>
+        <v>25.67704896844508</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -736,16 +736,16 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>12.41894186429753</v>
+        <v>6.039610913446428</v>
       </c>
       <c r="D10" t="n">
-        <v>10.71426411037301</v>
+        <v>7.674684372183226</v>
       </c>
       <c r="E10" t="n">
-        <v>26.45229551864099</v>
+        <v>25.43425113145828</v>
       </c>
       <c r="F10" t="n">
-        <v>26.6957650274269</v>
+        <v>25.67704896844508</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -768,16 +768,16 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>45.96256806182859</v>
+        <v>12.41894186429753</v>
       </c>
       <c r="D11" t="n">
-        <v>47.74829654774024</v>
+        <v>10.71426411037301</v>
       </c>
       <c r="E11" t="n">
-        <v>26.45229551864099</v>
+        <v>25.43425113145828</v>
       </c>
       <c r="F11" t="n">
-        <v>26.6957650274269</v>
+        <v>25.67704896844508</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -800,16 +800,16 @@
         <v>11</v>
       </c>
       <c r="C12" t="n">
-        <v>21.68478655599791</v>
+        <v>45.96256806182859</v>
       </c>
       <c r="D12" t="n">
-        <v>21.29026446666949</v>
+        <v>47.74829654774024</v>
       </c>
       <c r="E12" t="n">
-        <v>26.45229551864099</v>
+        <v>25.43425113145828</v>
       </c>
       <c r="F12" t="n">
-        <v>26.6957650274269</v>
+        <v>25.67704896844508</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -832,23 +832,55 @@
         <v>12</v>
       </c>
       <c r="C13" t="n">
+        <v>21.68478655599791</v>
+      </c>
+      <c r="D13" t="n">
+        <v>21.29026446666949</v>
+      </c>
+      <c r="E13" t="n">
+        <v>25.43425113145828</v>
+      </c>
+      <c r="F13" t="n">
+        <v>25.67704896844508</v>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>T0374</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>G1</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>W0017F0001T0006Z000C1N30.png</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>13</v>
+      </c>
+      <c r="C14" t="n">
         <v>54.81929739294412</v>
       </c>
-      <c r="D13" t="n">
+      <c r="D14" t="n">
         <v>53.58861990709174</v>
       </c>
-      <c r="E13" t="n">
-        <v>26.45229551864099</v>
-      </c>
-      <c r="F13" t="n">
-        <v>26.6957650274269</v>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>T0374</t>
-        </is>
-      </c>
-      <c r="H13" t="inlineStr">
+      <c r="E14" t="n">
+        <v>25.43425113145828</v>
+      </c>
+      <c r="F14" t="n">
+        <v>25.67704896844508</v>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>T0374</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
         <is>
           <t>G1</t>
         </is>

--- a/dataset_t6_grouped/results2/G1/G1_T0374_W0017F0001T0006Z000C1N30_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G1/G1_T0374_W0017F0001T0006Z000C1N30_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>104.5136875066879</v>
+        <v>16.98347421983678</v>
       </c>
       <c r="D2" t="n">
-        <v>105.3942007704006</v>
+        <v>17.12655762519011</v>
       </c>
       <c r="E2" t="n">
-        <v>25.43425113145828</v>
+        <v>4.133065808861971</v>
       </c>
       <c r="F2" t="n">
-        <v>25.67704896844508</v>
+        <v>4.172520457372325</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>36.19801209748254</v>
+        <v>5.882176965840913</v>
       </c>
       <c r="D3" t="n">
-        <v>35.15542394787635</v>
+        <v>5.712756391529907</v>
       </c>
       <c r="E3" t="n">
-        <v>25.43425113145828</v>
+        <v>4.133065808861971</v>
       </c>
       <c r="F3" t="n">
-        <v>25.67704896844508</v>
+        <v>4.172520457372325</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>30.87313071510012</v>
+        <v>5.016883741203769</v>
       </c>
       <c r="D4" t="n">
-        <v>29.56470169759898</v>
+        <v>4.804264025859834</v>
       </c>
       <c r="E4" t="n">
-        <v>25.43425113145828</v>
+        <v>4.133065808861971</v>
       </c>
       <c r="F4" t="n">
-        <v>25.67704896844508</v>
+        <v>4.172520457372325</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>22.15318102070701</v>
+        <v>3.59989191586489</v>
       </c>
       <c r="D5" t="n">
-        <v>20.84778765253281</v>
+        <v>3.387765493536581</v>
       </c>
       <c r="E5" t="n">
-        <v>25.43425113145828</v>
+        <v>4.133065808861971</v>
       </c>
       <c r="F5" t="n">
-        <v>25.67704896844508</v>
+        <v>4.172520457372325</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>30.00816557450127</v>
+        <v>4.876326905856457</v>
       </c>
       <c r="D6" t="n">
-        <v>28.30451177599641</v>
+        <v>4.599483163599417</v>
       </c>
       <c r="E6" t="n">
-        <v>25.43425113145828</v>
+        <v>4.133065808861971</v>
       </c>
       <c r="F6" t="n">
-        <v>25.67704896844508</v>
+        <v>4.172520457372325</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>35.52178965868286</v>
+        <v>5.772290819535965</v>
       </c>
       <c r="D7" t="n">
-        <v>35.96971709957152</v>
+        <v>5.845079028680372</v>
       </c>
       <c r="E7" t="n">
-        <v>25.43425113145828</v>
+        <v>4.133065808861971</v>
       </c>
       <c r="F7" t="n">
-        <v>25.67704896844508</v>
+        <v>4.172520457372325</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>10.72170223799552</v>
+        <v>1.742276613674271</v>
       </c>
       <c r="D8" t="n">
-        <v>12.14657995092263</v>
+        <v>1.973819242024927</v>
       </c>
       <c r="E8" t="n">
-        <v>25.43425113145828</v>
+        <v>4.133065808861971</v>
       </c>
       <c r="F8" t="n">
-        <v>25.67704896844508</v>
+        <v>4.172520457372325</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>5.787569291502646</v>
+        <v>0.9404800098691801</v>
       </c>
       <c r="D9" t="n">
-        <v>4.657974012814054</v>
+        <v>0.7569207770822838</v>
       </c>
       <c r="E9" t="n">
-        <v>25.43425113145828</v>
+        <v>4.133065808861971</v>
       </c>
       <c r="F9" t="n">
-        <v>25.67704896844508</v>
+        <v>4.172520457372325</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -736,16 +736,16 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>6.039610913446428</v>
+        <v>0.9814367734350447</v>
       </c>
       <c r="D10" t="n">
-        <v>7.674684372183226</v>
+        <v>1.247136210479774</v>
       </c>
       <c r="E10" t="n">
-        <v>25.43425113145828</v>
+        <v>4.133065808861971</v>
       </c>
       <c r="F10" t="n">
-        <v>25.67704896844508</v>
+        <v>4.172520457372325</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -768,16 +768,16 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>12.41894186429753</v>
+        <v>2.018078052948348</v>
       </c>
       <c r="D11" t="n">
-        <v>10.71426411037301</v>
+        <v>1.741067917935615</v>
       </c>
       <c r="E11" t="n">
-        <v>25.43425113145828</v>
+        <v>4.133065808861971</v>
       </c>
       <c r="F11" t="n">
-        <v>25.67704896844508</v>
+        <v>4.172520457372325</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -800,16 +800,16 @@
         <v>11</v>
       </c>
       <c r="C12" t="n">
-        <v>45.96256806182859</v>
+        <v>7.468917310047146</v>
       </c>
       <c r="D12" t="n">
-        <v>47.74829654774024</v>
+        <v>7.759098189007789</v>
       </c>
       <c r="E12" t="n">
-        <v>25.43425113145828</v>
+        <v>4.133065808861971</v>
       </c>
       <c r="F12" t="n">
-        <v>25.67704896844508</v>
+        <v>4.172520457372325</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -832,16 +832,16 @@
         <v>12</v>
       </c>
       <c r="C13" t="n">
-        <v>21.68478655599791</v>
+        <v>3.523777815349661</v>
       </c>
       <c r="D13" t="n">
-        <v>21.29026446666949</v>
+        <v>3.459667975833792</v>
       </c>
       <c r="E13" t="n">
-        <v>25.43425113145828</v>
+        <v>4.133065808861971</v>
       </c>
       <c r="F13" t="n">
-        <v>25.67704896844508</v>
+        <v>4.172520457372325</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -864,16 +864,16 @@
         <v>13</v>
       </c>
       <c r="C14" t="n">
-        <v>54.81929739294412</v>
+        <v>8.908135826353419</v>
       </c>
       <c r="D14" t="n">
-        <v>53.58861990709174</v>
+        <v>8.708150734902407</v>
       </c>
       <c r="E14" t="n">
-        <v>25.43425113145828</v>
+        <v>4.133065808861971</v>
       </c>
       <c r="F14" t="n">
-        <v>25.67704896844508</v>
+        <v>4.172520457372325</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
